--- a/artfynd/A 25534-2024 artfynd.xlsx
+++ b/artfynd/A 25534-2024 artfynd.xlsx
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118202062</v>
+        <v>118202326</v>
       </c>
       <c r="B12" t="n">
-        <v>5166</v>
+        <v>91124</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1801,32 +1801,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>1339</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1834,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583135</v>
+        <v>583080</v>
       </c>
       <c r="R12" t="n">
-        <v>6426905</v>
+        <v>6426910</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1874,7 +1876,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Klen undertryckt gran</t>
+          <t>På gammal tallåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,10 +1904,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118202326</v>
+        <v>118202062</v>
       </c>
       <c r="B13" t="n">
-        <v>91124</v>
+        <v>5166</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1918,34 +1920,32 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1339</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1953,10 +1953,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583080</v>
+        <v>583135</v>
       </c>
       <c r="R13" t="n">
-        <v>6426910</v>
+        <v>6426905</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal tallåga</t>
+          <t>Klen undertryckt gran</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 25534-2024 artfynd.xlsx
+++ b/artfynd/A 25534-2024 artfynd.xlsx
@@ -2579,7 +2579,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118488036</v>
+        <v>118488059</v>
       </c>
       <c r="B19" t="n">
         <v>97846</v>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2622,7 +2622,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -2631,10 +2635,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582707</v>
+        <v>582725</v>
       </c>
       <c r="R19" t="n">
-        <v>6427239</v>
+        <v>6427226</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2694,7 +2698,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118488059</v>
+        <v>118488036</v>
       </c>
       <c r="B20" t="n">
         <v>97846</v>
@@ -2729,7 +2733,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2737,11 +2741,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582725</v>
+        <v>582707</v>
       </c>
       <c r="R20" t="n">
-        <v>6427226</v>
+        <v>6427239</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 25534-2024 artfynd.xlsx
+++ b/artfynd/A 25534-2024 artfynd.xlsx
@@ -2582,7 +2582,7 @@
         <v>118488059</v>
       </c>
       <c r="B19" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>118488036</v>
       </c>
       <c r="B20" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>

--- a/artfynd/A 25534-2024 artfynd.xlsx
+++ b/artfynd/A 25534-2024 artfynd.xlsx
@@ -2579,7 +2579,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118488059</v>
+        <v>118488036</v>
       </c>
       <c r="B19" t="n">
         <v>97853</v>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2622,11 +2622,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -2635,10 +2631,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582725</v>
+        <v>582707</v>
       </c>
       <c r="R19" t="n">
-        <v>6427226</v>
+        <v>6427239</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2698,7 +2694,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118488036</v>
+        <v>118488059</v>
       </c>
       <c r="B20" t="n">
         <v>97853</v>
@@ -2733,7 +2729,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2741,7 +2737,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582707</v>
+        <v>582725</v>
       </c>
       <c r="R20" t="n">
-        <v>6427239</v>
+        <v>6427226</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 25534-2024 artfynd.xlsx
+++ b/artfynd/A 25534-2024 artfynd.xlsx
@@ -2000,7 +2000,7 @@
         <v>0</v>
       </c>
       <c r="AE13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
